--- a/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
@@ -7,19 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="16" state="visible" r:id="rId16"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,21 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -995,38 +1010,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1052,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.482</v>
+        <v>2.401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1048,6 +1063,234 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>560709.cif</t>
         </is>
       </c>
@@ -1060,27 +1303,194 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.601</v>
+        <v>2.515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1109,72 +1519,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.291</v>
+        <v>2.304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1185,284 +1595,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.332</v>
+        <v>2.323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.358</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.482</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.501</v>
+        <v>2.329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.499</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1473,173 +1640,6 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.538</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>300162.cif</t>
         </is>
       </c>

--- a/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
@@ -7,19 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="16" state="visible" r:id="rId16"/>
@@ -444,34 +444,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,9 +486,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.332</v>
+        <v>2.482</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -980,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1033,310 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>539016.cif</t>
         </is>
       </c>
@@ -1050,7 +1369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1079,57 +1398,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.358</v>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1140,314 +1459,162 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.401</v>
+        <v>2.495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.482</v>
+        <v>2.499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.501</v>
+        <v>2.515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300162.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.601</v>
+        <v>2.519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.482</v>
+        <v>2.304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.501</v>
+        <v>2.323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.482</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.499</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.515</v>
+        <v>2.329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1458,11 +1625,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1473,127 +1640,6 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.538</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>300162.cif</t>
         </is>
       </c>
@@ -1626,7 +1672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1655,52 +1701,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
           <t>1612190.cif</t>
         </is>
       </c>

--- a/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
@@ -10,23 +10,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,6 +775,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>300160.cif</t>
         </is>
       </c>
@@ -790,7 +884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -836,7 +930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -882,7 +976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -911,21 +1005,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>300163.cif</t>
         </is>
       </c>
@@ -943,7 +1098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -989,40 +1144,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1037,7 +1238,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.332</v>
+        <v>2.482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1045,95 +1246,79 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1329,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.482</v>
+        <v>2.401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1155,6 +1340,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>560709.cif</t>
         </is>
       </c>
@@ -1167,302 +1458,226 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.601</v>
+        <v>2.515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.482</v>
+        <v>2.304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.501</v>
+        <v>2.323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.358</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.482</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.501</v>
+        <v>2.329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.499</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1473,127 +1688,6 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.539</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>300162.cif</t>
         </is>
       </c>

--- a/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
@@ -7,21 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,15 +469,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.358</v>
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.401</v>
+        <v>2.482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -499,11 +499,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.482</v>
+        <v>2.501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -512,61 +512,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+        <v>2.461</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.053</v>
+      </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.469</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1637,6 +1607,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1660,11 +1763,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.401</v>
+        <v>2.979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1675,26 +1778,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>539016.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.482</v>
+        <v>3.291</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.501</v>
+        <v>3.332</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1714,7 +1817,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.461</v>
+        <v>3.201</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -1725,7 +1828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.053</v>
+        <v>0.193</v>
       </c>
       <c r="C7" t="inlineStr"/>
     </row>
@@ -1734,7 +1837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1816,109 +1919,6 @@
         <v>0.25</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.291</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.201</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="In-In" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="U-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_site_pairs.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="In-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="U-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,46 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.461</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.496</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1259,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,15 +1297,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>539016.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.401</v>
+        <v>2.358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1316,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.482</v>
+        <v>2.401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1312,11 +1327,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.501</v>
+        <v>2.482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1327,44 +1342,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>539016.cif</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>2.601</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.496</v>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1607,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,15 +1660,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.358</v>
+        <v>2.979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1679,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.401</v>
+        <v>3.332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1658,76 +1688,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.482</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+        <v>3.156</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.469</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1843,7 +1828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,11 +1851,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.979</v>
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1885,7 +1870,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.332</v>
+        <v>2.482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1894,31 +1879,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.156</v>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2079,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,11 +2102,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.233</v>
+        <v>3.12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2115,121 +2115,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+        <v>3.12</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2242,7 +2150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2265,42 +2173,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>300156.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Full occupancy</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.323</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
